--- a/basedatos.xlsx
+++ b/basedatos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\CRM SIERRA MORENA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -763,7 +763,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
@@ -786,7 +786,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>21</v>
@@ -870,7 +870,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
@@ -912,7 +912,7 @@
         <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
@@ -973,7 +973,7 @@
         <v>34</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>26</v>
@@ -1015,7 +1015,7 @@
         <v>46</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>17</v>
@@ -1225,7 +1225,7 @@
         <v>86</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>26</v>
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>64</v>
@@ -1878,7 +1878,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>76</v>

--- a/basedatos.xlsx
+++ b/basedatos.xlsx
@@ -1092,11 +1092,11 @@
         <v>3</v>
       </c>
       <c r="G10" s="7">
-        <v>46046</v>
+        <v>46122</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>16</v>
@@ -1134,11 +1134,11 @@
         <v>3</v>
       </c>
       <c r="G11" s="8">
-        <v>46036</v>
+        <v>46126</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>16</v>
@@ -1176,11 +1176,11 @@
         <v>3</v>
       </c>
       <c r="G12" s="7">
-        <v>46100</v>
+        <v>46127</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>22</v>
@@ -1344,11 +1344,11 @@
         <v>3</v>
       </c>
       <c r="G16" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>16</v>
@@ -1596,11 +1596,11 @@
         <v>3</v>
       </c>
       <c r="G22" s="7">
-        <v>46032</v>
+        <v>46122</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>22</v>
@@ -1638,11 +1638,11 @@
         <v>3</v>
       </c>
       <c r="G23" s="8">
-        <v>46093</v>
+        <v>46124</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>16</v>
@@ -1680,11 +1680,11 @@
         <v>3</v>
       </c>
       <c r="G24" s="8">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>22</v>
